--- a/Tong Hop.xlsx
+++ b/Tong Hop.xlsx
@@ -2,15 +2,15 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
-  <workbookPr defaultThemeVersion="202300"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\1. TCKT_PCVT\4. Công nghệ AI\Các báo cáo\SCL\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\DATA\DATA_SCL\BC_SCL\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8979B0D0-F6FD-4BDE-AB98-75FB369C7EBB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EC6E685F-F3D7-48DA-A061-C412627FE16A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{EA8CD95B-BEDE-4E99-A9CD-4372C7F6DBD0}"/>
+    <workbookView xWindow="1100" yWindow="1100" windowWidth="21600" windowHeight="12710" xr2:uid="{EA8CD95B-BEDE-4E99-A9CD-4372C7F6DBD0}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -27,8 +27,6 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
     <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
@@ -166,8 +164,8 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="2">
-    <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="169" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="164" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="165" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;??_-;_-@_-"/>
   </numFmts>
   <fonts count="8" x14ac:knownFonts="1">
     <font>
@@ -325,10 +323,10 @@
   </borders>
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
@@ -339,10 +337,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -351,7 +346,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="169" fontId="2" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -363,7 +358,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="169" fontId="3" fillId="0" borderId="7" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="3" fillId="0" borderId="7" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -381,10 +376,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -395,28 +387,12 @@
   </cellStyles>
   <dxfs count="17">
     <dxf>
-      <alignment vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top/>
-        <bottom/>
-      </border>
-    </dxf>
-    <dxf>
       <font>
         <color rgb="FF1F1F1F"/>
         <name val="Arial"/>
         <family val="2"/>
       </font>
-      <numFmt numFmtId="169" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;??_-;_-@_-"/>
+      <numFmt numFmtId="165" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;??_-;_-@_-"/>
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="1"/>
       <border diagonalUp="0" diagonalDown="0" outline="0">
         <left style="thin">
@@ -439,7 +415,7 @@
         <name val="Arial"/>
         <family val="2"/>
       </font>
-      <numFmt numFmtId="169" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;??_-;_-@_-"/>
+      <numFmt numFmtId="165" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;??_-;_-@_-"/>
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="1"/>
       <border diagonalUp="0" diagonalDown="0" outline="0">
         <left style="thin">
@@ -539,7 +515,7 @@
         <family val="2"/>
         <scheme val="none"/>
       </font>
-      <numFmt numFmtId="169" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;??_-;_-@_-"/>
+      <numFmt numFmtId="165" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;??_-;_-@_-"/>
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="1"/>
       <border diagonalUp="0" diagonalDown="0" outline="0">
         <left style="thin">
@@ -793,6 +769,25 @@
       </border>
     </dxf>
     <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0"/>
+    </dxf>
+    <dxf>
       <border>
         <bottom style="thin">
           <color indexed="64"/>
@@ -800,19 +795,16 @@
       </border>
     </dxf>
     <dxf>
-      <border diagonalUp="0" diagonalDown="0">
+      <alignment vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
         <left style="thin">
           <color indexed="64"/>
         </left>
         <right style="thin">
           <color indexed="64"/>
         </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
+        <top/>
+        <bottom/>
       </border>
     </dxf>
   </dxfs>
@@ -829,21 +821,21 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{F1AB6DDC-BA93-481E-BD2B-9DF8058E8584}" name="Table1" displayName="Table1" ref="A1:L9" totalsRowShown="0" headerRowDxfId="1" dataDxfId="0" headerRowBorderDxfId="15" tableBorderDxfId="16" totalsRowBorderDxfId="14">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{F1AB6DDC-BA93-481E-BD2B-9DF8058E8584}" name="Table1" displayName="Table1" ref="A1:L9" totalsRowShown="0" headerRowDxfId="16" dataDxfId="14" headerRowBorderDxfId="15" tableBorderDxfId="13" totalsRowBorderDxfId="12">
   <autoFilter ref="A1:L9" xr:uid="{F1AB6DDC-BA93-481E-BD2B-9DF8058E8584}"/>
   <tableColumns count="12">
-    <tableColumn id="1" xr3:uid="{DAC04565-69BC-4CDF-9E0A-EC1119831221}" name="STT" dataDxfId="13"/>
-    <tableColumn id="2" xr3:uid="{D6161F9A-87AA-431B-80BE-36A93E2AFC54}" name="Mã công trình" dataDxfId="12"/>
-    <tableColumn id="3" xr3:uid="{B6921986-DEFB-4044-8199-A3891359D0D8}" name="Tên công trình" dataDxfId="11"/>
-    <tableColumn id="10" xr3:uid="{1BF7E3F8-25B1-4DF4-B523-310B52CF464E}" name="Số QĐ phê duyệt danh mục" dataDxfId="10" dataCellStyle="Normal 2"/>
-    <tableColumn id="11" xr3:uid="{3AE98590-A534-40D4-A68D-3A7A411590AD}" name="Nội dung chính sữa chữa " dataDxfId="9" dataCellStyle="Normal 2"/>
-    <tableColumn id="12" xr3:uid="{465F0A31-3F91-4822-BA14-948A18D11083}" name="Tiến độ thực hiện theo kế hoạch" dataDxfId="8" dataCellStyle="Normal 2"/>
-    <tableColumn id="4" xr3:uid="{CA856511-17A6-4630-B6ED-3630EBCB18AF}" name="Năm" dataDxfId="7"/>
-    <tableColumn id="5" xr3:uid="{8E900E18-E817-403C-991D-0FB1E7E5763A}" name="Giá trị khái toán" dataDxfId="6" dataCellStyle="Comma"/>
-    <tableColumn id="6" xr3:uid="{F1B544CF-5D4E-4E6C-834E-112E2E2B9814}" name="Tên hạng mục" dataDxfId="5"/>
-    <tableColumn id="7" xr3:uid="{AEFAD23C-45D2-400E-AB7E-19B2CD7F4803}" name="Trạng thái" dataDxfId="4"/>
-    <tableColumn id="8" xr3:uid="{2675D14E-65F9-45FF-90BF-967C376D3844}" name="Giá trị thực hiện" dataDxfId="3" dataCellStyle="Comma"/>
-    <tableColumn id="9" xr3:uid="{695670EC-1745-48D9-9A74-4408C2464719}" name="Giá trị quyết toán" dataDxfId="2" dataCellStyle="Comma"/>
+    <tableColumn id="1" xr3:uid="{DAC04565-69BC-4CDF-9E0A-EC1119831221}" name="STT" dataDxfId="11"/>
+    <tableColumn id="2" xr3:uid="{D6161F9A-87AA-431B-80BE-36A93E2AFC54}" name="Mã công trình" dataDxfId="10"/>
+    <tableColumn id="3" xr3:uid="{B6921986-DEFB-4044-8199-A3891359D0D8}" name="Tên công trình" dataDxfId="9"/>
+    <tableColumn id="10" xr3:uid="{1BF7E3F8-25B1-4DF4-B523-310B52CF464E}" name="Số QĐ phê duyệt danh mục" dataDxfId="8" dataCellStyle="Normal 2"/>
+    <tableColumn id="11" xr3:uid="{3AE98590-A534-40D4-A68D-3A7A411590AD}" name="Nội dung chính sữa chữa " dataDxfId="7" dataCellStyle="Normal 2"/>
+    <tableColumn id="12" xr3:uid="{465F0A31-3F91-4822-BA14-948A18D11083}" name="Tiến độ thực hiện theo kế hoạch" dataDxfId="6" dataCellStyle="Normal 2"/>
+    <tableColumn id="4" xr3:uid="{CA856511-17A6-4630-B6ED-3630EBCB18AF}" name="Năm" dataDxfId="5"/>
+    <tableColumn id="5" xr3:uid="{8E900E18-E817-403C-991D-0FB1E7E5763A}" name="Giá trị khái toán" dataDxfId="4" dataCellStyle="Comma"/>
+    <tableColumn id="6" xr3:uid="{F1B544CF-5D4E-4E6C-834E-112E2E2B9814}" name="Tên hạng mục" dataDxfId="3"/>
+    <tableColumn id="7" xr3:uid="{AEFAD23C-45D2-400E-AB7E-19B2CD7F4803}" name="Trạng thái" dataDxfId="2"/>
+    <tableColumn id="8" xr3:uid="{2675D14E-65F9-45FF-90BF-967C376D3844}" name="Giá trị thực hiện" dataDxfId="1" dataCellStyle="Comma"/>
+    <tableColumn id="9" xr3:uid="{695670EC-1745-48D9-9A74-4408C2464719}" name="Giá trị quyết toán" dataDxfId="0" dataCellStyle="Comma"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1167,23 +1159,23 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B84B92FB-9617-4ECC-974D-88D4E382CA3F}">
   <dimension ref="A1:L9"/>
-  <sheetFormatPr defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="8.83203125" defaultRowHeight="15.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="6.5" style="16" customWidth="1"/>
-    <col min="2" max="2" width="15.796875" style="15" customWidth="1"/>
-    <col min="3" max="3" width="29.69921875" style="15" customWidth="1"/>
-    <col min="4" max="4" width="15.796875" style="15" customWidth="1"/>
-    <col min="5" max="5" width="28.3984375" style="17" customWidth="1"/>
-    <col min="6" max="6" width="14.59765625" style="15" customWidth="1"/>
-    <col min="7" max="7" width="7.09765625" style="15" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="18" style="15" customWidth="1"/>
-    <col min="9" max="9" width="19.09765625" style="15" customWidth="1"/>
-    <col min="10" max="11" width="18.3984375" style="15" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="16.09765625" style="15" customWidth="1"/>
-    <col min="13" max="16384" width="8.796875" style="15"/>
+    <col min="1" max="1" width="6.5" style="15" customWidth="1"/>
+    <col min="2" max="2" width="15.83203125" style="14" customWidth="1"/>
+    <col min="3" max="3" width="29.6640625" style="14" customWidth="1"/>
+    <col min="4" max="4" width="15.83203125" style="14" customWidth="1"/>
+    <col min="5" max="5" width="28.4140625" style="16" customWidth="1"/>
+    <col min="6" max="6" width="14.58203125" style="14" customWidth="1"/>
+    <col min="7" max="7" width="7.08203125" style="14" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="18" style="14" customWidth="1"/>
+    <col min="9" max="9" width="19.08203125" style="14" customWidth="1"/>
+    <col min="10" max="11" width="18.4140625" style="14" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="16.08203125" style="14" customWidth="1"/>
+    <col min="13" max="16384" width="8.83203125" style="14"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:12" ht="15.65" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1193,13 +1185,13 @@
       <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="14" t="s">
+      <c r="D1" s="13" t="s">
         <v>32</v>
       </c>
-      <c r="E1" s="14" t="s">
+      <c r="E1" s="13" t="s">
         <v>33</v>
       </c>
-      <c r="F1" s="14" t="s">
+      <c r="F1" s="13" t="s">
         <v>37</v>
       </c>
       <c r="G1" s="2" t="s">
@@ -1214,252 +1206,260 @@
       <c r="J1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="K1" s="4" t="s">
+      <c r="K1" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="L1" s="5" t="s">
+      <c r="L1" s="4" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="2" spans="1:12" ht="30" x14ac:dyDescent="0.3">
-      <c r="A2" s="6">
+    <row r="2" spans="1:12" ht="46.5" x14ac:dyDescent="0.35">
+      <c r="A2" s="5">
         <v>1</v>
       </c>
-      <c r="B2" s="7" t="s">
+      <c r="B2" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="C2" s="7" t="s">
+      <c r="C2" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="D2" s="14"/>
-      <c r="E2" s="14"/>
-      <c r="F2" s="14"/>
-      <c r="G2" s="7">
+      <c r="D2" s="13"/>
+      <c r="E2" s="13"/>
+      <c r="F2" s="13"/>
+      <c r="G2" s="6">
         <v>2026</v>
       </c>
-      <c r="H2" s="8">
+      <c r="H2" s="7">
         <v>12552889759</v>
       </c>
-      <c r="I2" s="7" t="s">
+      <c r="I2" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="J2" s="7" t="s">
+      <c r="J2" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="K2" s="8"/>
-      <c r="L2" s="8"/>
+      <c r="K2" s="7">
+        <v>5000000000</v>
+      </c>
+      <c r="L2" s="7"/>
     </row>
-    <row r="3" spans="1:12" ht="60" x14ac:dyDescent="0.3">
-      <c r="A3" s="6">
+    <row r="3" spans="1:12" ht="62" x14ac:dyDescent="0.35">
+      <c r="A3" s="5">
         <v>2</v>
       </c>
-      <c r="B3" s="7" t="s">
+      <c r="B3" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="C3" s="7" t="s">
+      <c r="C3" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="D3" s="13" t="s">
+      <c r="D3" s="12" t="s">
         <v>34</v>
       </c>
-      <c r="E3" s="13"/>
-      <c r="F3" s="13"/>
-      <c r="G3" s="7">
+      <c r="E3" s="12"/>
+      <c r="F3" s="12"/>
+      <c r="G3" s="6">
         <v>2026</v>
       </c>
-      <c r="H3" s="8">
+      <c r="H3" s="7">
         <v>13650367159</v>
       </c>
-      <c r="I3" s="7" t="s">
+      <c r="I3" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="J3" s="7" t="s">
+      <c r="J3" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="K3" s="8">
+      <c r="K3" s="7">
         <v>1347233815</v>
       </c>
-      <c r="L3" s="8"/>
+      <c r="L3" s="7"/>
     </row>
-    <row r="4" spans="1:12" ht="46.8" x14ac:dyDescent="0.3">
-      <c r="A4" s="6">
+    <row r="4" spans="1:12" ht="46.5" x14ac:dyDescent="0.35">
+      <c r="A4" s="5">
         <v>3</v>
       </c>
-      <c r="B4" s="7" t="s">
+      <c r="B4" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="C4" s="7" t="s">
+      <c r="C4" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="D4" s="13" t="s">
+      <c r="D4" s="12" t="s">
         <v>34</v>
       </c>
-      <c r="E4" s="13" t="s">
+      <c r="E4" s="12" t="s">
         <v>35</v>
       </c>
-      <c r="F4" s="13" t="s">
+      <c r="F4" s="12" t="s">
         <v>38</v>
       </c>
-      <c r="G4" s="7">
+      <c r="G4" s="6">
         <v>2026</v>
       </c>
-      <c r="H4" s="8">
+      <c r="H4" s="7">
         <v>3765771568</v>
       </c>
-      <c r="I4" s="7" t="s">
+      <c r="I4" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="J4" s="7" t="s">
+      <c r="J4" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="K4" s="8"/>
-      <c r="L4" s="8"/>
+      <c r="K4" s="7">
+        <v>3000000000</v>
+      </c>
+      <c r="L4" s="7"/>
     </row>
-    <row r="5" spans="1:12" ht="45" x14ac:dyDescent="0.3">
-      <c r="A5" s="6">
+    <row r="5" spans="1:12" ht="46.5" x14ac:dyDescent="0.35">
+      <c r="A5" s="5">
         <v>4</v>
       </c>
-      <c r="B5" s="7" t="s">
+      <c r="B5" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="C5" s="7" t="s">
+      <c r="C5" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="D5" s="13"/>
-      <c r="E5" s="18"/>
-      <c r="F5" s="18"/>
-      <c r="G5" s="7">
+      <c r="D5" s="12"/>
+      <c r="E5" s="12"/>
+      <c r="F5" s="12"/>
+      <c r="G5" s="6">
         <v>2026</v>
       </c>
-      <c r="H5" s="8">
+      <c r="H5" s="7">
         <v>1590994000</v>
       </c>
-      <c r="I5" s="7" t="s">
+      <c r="I5" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="J5" s="7" t="s">
+      <c r="J5" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="K5" s="8"/>
-      <c r="L5" s="8"/>
+      <c r="K5" s="7">
+        <v>1000000000</v>
+      </c>
+      <c r="L5" s="7"/>
     </row>
-    <row r="6" spans="1:12" ht="30" x14ac:dyDescent="0.3">
-      <c r="A6" s="6">
+    <row r="6" spans="1:12" ht="31" x14ac:dyDescent="0.35">
+      <c r="A6" s="5">
         <v>5</v>
       </c>
-      <c r="B6" s="7" t="s">
+      <c r="B6" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="C6" s="7" t="s">
+      <c r="C6" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="D6" s="13" t="s">
+      <c r="D6" s="12" t="s">
         <v>34</v>
       </c>
-      <c r="E6" s="13"/>
-      <c r="F6" s="13"/>
-      <c r="G6" s="7">
+      <c r="E6" s="12"/>
+      <c r="F6" s="12"/>
+      <c r="G6" s="6">
         <v>2026</v>
       </c>
-      <c r="H6" s="8">
+      <c r="H6" s="7">
         <v>526699800</v>
       </c>
-      <c r="I6" s="7" t="s">
+      <c r="I6" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="J6" s="7" t="s">
+      <c r="J6" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="K6" s="8"/>
-      <c r="L6" s="8"/>
+      <c r="K6" s="7"/>
+      <c r="L6" s="7"/>
     </row>
-    <row r="7" spans="1:12" ht="46.8" x14ac:dyDescent="0.3">
-      <c r="A7" s="6">
+    <row r="7" spans="1:12" ht="46.5" x14ac:dyDescent="0.35">
+      <c r="A7" s="5">
         <v>6</v>
       </c>
-      <c r="B7" s="7" t="s">
+      <c r="B7" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="C7" s="7" t="s">
+      <c r="C7" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="D7" s="13" t="s">
+      <c r="D7" s="12" t="s">
         <v>34</v>
       </c>
-      <c r="E7" s="13" t="s">
+      <c r="E7" s="12" t="s">
         <v>36</v>
       </c>
-      <c r="F7" s="13" t="s">
+      <c r="F7" s="12" t="s">
         <v>38</v>
       </c>
-      <c r="G7" s="7">
+      <c r="G7" s="6">
         <v>2026</v>
       </c>
-      <c r="H7" s="8">
+      <c r="H7" s="7">
         <v>13236612376</v>
       </c>
-      <c r="I7" s="7" t="s">
+      <c r="I7" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="J7" s="7" t="s">
+      <c r="J7" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="K7" s="8"/>
-      <c r="L7" s="8"/>
+      <c r="K7" s="7">
+        <v>5000000000</v>
+      </c>
+      <c r="L7" s="7"/>
     </row>
-    <row r="8" spans="1:12" ht="45" x14ac:dyDescent="0.3">
-      <c r="A8" s="6">
+    <row r="8" spans="1:12" ht="46.5" x14ac:dyDescent="0.35">
+      <c r="A8" s="5">
         <v>7</v>
       </c>
-      <c r="B8" s="7" t="s">
+      <c r="B8" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="C8" s="7" t="s">
+      <c r="C8" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="D8" s="13"/>
-      <c r="E8" s="18" t="s">
+      <c r="D8" s="12"/>
+      <c r="E8" s="12" t="s">
         <v>28</v>
       </c>
-      <c r="F8" s="18" t="s">
+      <c r="F8" s="12" t="s">
         <v>39</v>
       </c>
-      <c r="G8" s="7">
+      <c r="G8" s="6">
         <v>2026</v>
       </c>
-      <c r="H8" s="8">
+      <c r="H8" s="7">
         <v>5780025934</v>
       </c>
-      <c r="I8" s="7" t="s">
+      <c r="I8" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="J8" s="7" t="s">
+      <c r="J8" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="K8" s="8"/>
-      <c r="L8" s="8"/>
+      <c r="K8" s="7"/>
+      <c r="L8" s="7"/>
     </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A9" s="9"/>
-      <c r="B9" s="10"/>
-      <c r="C9" s="11" t="s">
+    <row r="9" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A9" s="8"/>
+      <c r="B9" s="9"/>
+      <c r="C9" s="10" t="s">
         <v>29</v>
       </c>
-      <c r="D9" s="13"/>
-      <c r="E9" s="19"/>
-      <c r="F9" s="19"/>
-      <c r="G9" s="10"/>
-      <c r="H9" s="12">
+      <c r="D9" s="12"/>
+      <c r="E9" s="17"/>
+      <c r="F9" s="17"/>
+      <c r="G9" s="9"/>
+      <c r="H9" s="11">
         <f>SUM(H2:H8)</f>
         <v>51103360596</v>
       </c>
-      <c r="I9" s="10"/>
-      <c r="J9" s="10"/>
-      <c r="K9" s="12">
+      <c r="I9" s="9"/>
+      <c r="J9" s="9"/>
+      <c r="K9" s="11">
         <f t="shared" ref="K9:L9" si="0">SUM(K2:K8)</f>
-        <v>1347233815</v>
-      </c>
-      <c r="L9" s="12">
+        <v>15347233815</v>
+      </c>
+      <c r="L9" s="11">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>

--- a/Tong Hop.xlsx
+++ b/Tong Hop.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\DATA\DATA_SCL\BC_SCL\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EC6E685F-F3D7-48DA-A061-C412627FE16A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{40A1425A-2DF6-448A-AEC2-886593801A7A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1100" yWindow="1100" windowWidth="21600" windowHeight="12710" xr2:uid="{EA8CD95B-BEDE-4E99-A9CD-4372C7F6DBD0}"/>
   </bookViews>
@@ -1239,9 +1239,11 @@
         <v>10</v>
       </c>
       <c r="K2" s="7">
-        <v>5000000000</v>
-      </c>
-      <c r="L2" s="7"/>
+        <v>10000000000</v>
+      </c>
+      <c r="L2" s="7">
+        <v>10000000000</v>
+      </c>
     </row>
     <row r="3" spans="1:12" ht="62" x14ac:dyDescent="0.35">
       <c r="A3" s="5">
@@ -1273,7 +1275,9 @@
       <c r="K3" s="7">
         <v>1347233815</v>
       </c>
-      <c r="L3" s="7"/>
+      <c r="L3" s="7">
+        <v>1347233815</v>
+      </c>
     </row>
     <row r="4" spans="1:12" ht="46.5" x14ac:dyDescent="0.35">
       <c r="A4" s="5">
@@ -1309,7 +1313,9 @@
       <c r="K4" s="7">
         <v>3000000000</v>
       </c>
-      <c r="L4" s="7"/>
+      <c r="L4" s="7">
+        <v>3000000000</v>
+      </c>
     </row>
     <row r="5" spans="1:12" ht="46.5" x14ac:dyDescent="0.35">
       <c r="A5" s="5">
@@ -1339,7 +1345,9 @@
       <c r="K5" s="7">
         <v>1000000000</v>
       </c>
-      <c r="L5" s="7"/>
+      <c r="L5" s="7">
+        <v>1000000000</v>
+      </c>
     </row>
     <row r="6" spans="1:12" ht="31" x14ac:dyDescent="0.35">
       <c r="A6" s="5">
@@ -1368,8 +1376,12 @@
       <c r="J6" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="K6" s="7"/>
-      <c r="L6" s="7"/>
+      <c r="K6" s="7">
+        <v>500000000</v>
+      </c>
+      <c r="L6" s="7">
+        <v>500000000</v>
+      </c>
     </row>
     <row r="7" spans="1:12" ht="46.5" x14ac:dyDescent="0.35">
       <c r="A7" s="5">
@@ -1405,7 +1417,9 @@
       <c r="K7" s="7">
         <v>5000000000</v>
       </c>
-      <c r="L7" s="7"/>
+      <c r="L7" s="7">
+        <v>5000000000</v>
+      </c>
     </row>
     <row r="8" spans="1:12" ht="46.5" x14ac:dyDescent="0.35">
       <c r="A8" s="5">
@@ -1436,8 +1450,12 @@
       <c r="J8" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="K8" s="7"/>
-      <c r="L8" s="7"/>
+      <c r="K8" s="7">
+        <v>5000000000</v>
+      </c>
+      <c r="L8" s="7">
+        <v>5000000000</v>
+      </c>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A9" s="8"/>
@@ -1457,11 +1475,11 @@
       <c r="J9" s="9"/>
       <c r="K9" s="11">
         <f t="shared" ref="K9:L9" si="0">SUM(K2:K8)</f>
-        <v>15347233815</v>
+        <v>25847233815</v>
       </c>
       <c r="L9" s="11">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>25847233815</v>
       </c>
     </row>
   </sheetData>

--- a/Tong Hop.xlsx
+++ b/Tong Hop.xlsx
@@ -2,15 +2,15 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
-  <workbookPr/>
+  <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\DATA\DATA_SCL\BC_SCL\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\1. TCKT_PCVT\4. Công nghệ AI\Các báo cáo\SCL\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{40A1425A-2DF6-448A-AEC2-886593801A7A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8979B0D0-F6FD-4BDE-AB98-75FB369C7EBB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1100" yWindow="1100" windowWidth="21600" windowHeight="12710" xr2:uid="{EA8CD95B-BEDE-4E99-A9CD-4372C7F6DBD0}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{EA8CD95B-BEDE-4E99-A9CD-4372C7F6DBD0}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -27,6 +27,8 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
     <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
@@ -164,8 +166,8 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="2">
-    <numFmt numFmtId="164" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="165" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="169" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;??_-;_-@_-"/>
   </numFmts>
   <fonts count="8" x14ac:knownFonts="1">
     <font>
@@ -323,10 +325,10 @@
   </borders>
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
@@ -337,7 +339,10 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -346,7 +351,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="169" fontId="2" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -358,7 +363,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="165" fontId="3" fillId="0" borderId="7" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="169" fontId="3" fillId="0" borderId="7" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -376,7 +381,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -387,12 +395,28 @@
   </cellStyles>
   <dxfs count="17">
     <dxf>
+      <alignment vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top/>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
       <font>
         <color rgb="FF1F1F1F"/>
         <name val="Arial"/>
         <family val="2"/>
       </font>
-      <numFmt numFmtId="165" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;??_-;_-@_-"/>
+      <numFmt numFmtId="169" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;??_-;_-@_-"/>
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="1"/>
       <border diagonalUp="0" diagonalDown="0" outline="0">
         <left style="thin">
@@ -415,7 +439,7 @@
         <name val="Arial"/>
         <family val="2"/>
       </font>
-      <numFmt numFmtId="165" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;??_-;_-@_-"/>
+      <numFmt numFmtId="169" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;??_-;_-@_-"/>
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="1"/>
       <border diagonalUp="0" diagonalDown="0" outline="0">
         <left style="thin">
@@ -515,7 +539,7 @@
         <family val="2"/>
         <scheme val="none"/>
       </font>
-      <numFmt numFmtId="165" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;??_-;_-@_-"/>
+      <numFmt numFmtId="169" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;??_-;_-@_-"/>
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="1"/>
       <border diagonalUp="0" diagonalDown="0" outline="0">
         <left style="thin">
@@ -769,6 +793,13 @@
       </border>
     </dxf>
     <dxf>
+      <border>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
       <border diagonalUp="0" diagonalDown="0">
         <left style="thin">
           <color indexed="64"/>
@@ -782,29 +813,6 @@
         <bottom style="thin">
           <color indexed="64"/>
         </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0"/>
-    </dxf>
-    <dxf>
-      <border>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top/>
-        <bottom/>
       </border>
     </dxf>
   </dxfs>
@@ -821,21 +829,21 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{F1AB6DDC-BA93-481E-BD2B-9DF8058E8584}" name="Table1" displayName="Table1" ref="A1:L9" totalsRowShown="0" headerRowDxfId="16" dataDxfId="14" headerRowBorderDxfId="15" tableBorderDxfId="13" totalsRowBorderDxfId="12">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{F1AB6DDC-BA93-481E-BD2B-9DF8058E8584}" name="Table1" displayName="Table1" ref="A1:L9" totalsRowShown="0" headerRowDxfId="1" dataDxfId="0" headerRowBorderDxfId="15" tableBorderDxfId="16" totalsRowBorderDxfId="14">
   <autoFilter ref="A1:L9" xr:uid="{F1AB6DDC-BA93-481E-BD2B-9DF8058E8584}"/>
   <tableColumns count="12">
-    <tableColumn id="1" xr3:uid="{DAC04565-69BC-4CDF-9E0A-EC1119831221}" name="STT" dataDxfId="11"/>
-    <tableColumn id="2" xr3:uid="{D6161F9A-87AA-431B-80BE-36A93E2AFC54}" name="Mã công trình" dataDxfId="10"/>
-    <tableColumn id="3" xr3:uid="{B6921986-DEFB-4044-8199-A3891359D0D8}" name="Tên công trình" dataDxfId="9"/>
-    <tableColumn id="10" xr3:uid="{1BF7E3F8-25B1-4DF4-B523-310B52CF464E}" name="Số QĐ phê duyệt danh mục" dataDxfId="8" dataCellStyle="Normal 2"/>
-    <tableColumn id="11" xr3:uid="{3AE98590-A534-40D4-A68D-3A7A411590AD}" name="Nội dung chính sữa chữa " dataDxfId="7" dataCellStyle="Normal 2"/>
-    <tableColumn id="12" xr3:uid="{465F0A31-3F91-4822-BA14-948A18D11083}" name="Tiến độ thực hiện theo kế hoạch" dataDxfId="6" dataCellStyle="Normal 2"/>
-    <tableColumn id="4" xr3:uid="{CA856511-17A6-4630-B6ED-3630EBCB18AF}" name="Năm" dataDxfId="5"/>
-    <tableColumn id="5" xr3:uid="{8E900E18-E817-403C-991D-0FB1E7E5763A}" name="Giá trị khái toán" dataDxfId="4" dataCellStyle="Comma"/>
-    <tableColumn id="6" xr3:uid="{F1B544CF-5D4E-4E6C-834E-112E2E2B9814}" name="Tên hạng mục" dataDxfId="3"/>
-    <tableColumn id="7" xr3:uid="{AEFAD23C-45D2-400E-AB7E-19B2CD7F4803}" name="Trạng thái" dataDxfId="2"/>
-    <tableColumn id="8" xr3:uid="{2675D14E-65F9-45FF-90BF-967C376D3844}" name="Giá trị thực hiện" dataDxfId="1" dataCellStyle="Comma"/>
-    <tableColumn id="9" xr3:uid="{695670EC-1745-48D9-9A74-4408C2464719}" name="Giá trị quyết toán" dataDxfId="0" dataCellStyle="Comma"/>
+    <tableColumn id="1" xr3:uid="{DAC04565-69BC-4CDF-9E0A-EC1119831221}" name="STT" dataDxfId="13"/>
+    <tableColumn id="2" xr3:uid="{D6161F9A-87AA-431B-80BE-36A93E2AFC54}" name="Mã công trình" dataDxfId="12"/>
+    <tableColumn id="3" xr3:uid="{B6921986-DEFB-4044-8199-A3891359D0D8}" name="Tên công trình" dataDxfId="11"/>
+    <tableColumn id="10" xr3:uid="{1BF7E3F8-25B1-4DF4-B523-310B52CF464E}" name="Số QĐ phê duyệt danh mục" dataDxfId="10" dataCellStyle="Normal 2"/>
+    <tableColumn id="11" xr3:uid="{3AE98590-A534-40D4-A68D-3A7A411590AD}" name="Nội dung chính sữa chữa " dataDxfId="9" dataCellStyle="Normal 2"/>
+    <tableColumn id="12" xr3:uid="{465F0A31-3F91-4822-BA14-948A18D11083}" name="Tiến độ thực hiện theo kế hoạch" dataDxfId="8" dataCellStyle="Normal 2"/>
+    <tableColumn id="4" xr3:uid="{CA856511-17A6-4630-B6ED-3630EBCB18AF}" name="Năm" dataDxfId="7"/>
+    <tableColumn id="5" xr3:uid="{8E900E18-E817-403C-991D-0FB1E7E5763A}" name="Giá trị khái toán" dataDxfId="6" dataCellStyle="Comma"/>
+    <tableColumn id="6" xr3:uid="{F1B544CF-5D4E-4E6C-834E-112E2E2B9814}" name="Tên hạng mục" dataDxfId="5"/>
+    <tableColumn id="7" xr3:uid="{AEFAD23C-45D2-400E-AB7E-19B2CD7F4803}" name="Trạng thái" dataDxfId="4"/>
+    <tableColumn id="8" xr3:uid="{2675D14E-65F9-45FF-90BF-967C376D3844}" name="Giá trị thực hiện" dataDxfId="3" dataCellStyle="Comma"/>
+    <tableColumn id="9" xr3:uid="{695670EC-1745-48D9-9A74-4408C2464719}" name="Giá trị quyết toán" dataDxfId="2" dataCellStyle="Comma"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1159,23 +1167,23 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B84B92FB-9617-4ECC-974D-88D4E382CA3F}">
   <dimension ref="A1:L9"/>
-  <sheetFormatPr defaultColWidth="8.83203125" defaultRowHeight="15.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="6.5" style="15" customWidth="1"/>
-    <col min="2" max="2" width="15.83203125" style="14" customWidth="1"/>
-    <col min="3" max="3" width="29.6640625" style="14" customWidth="1"/>
-    <col min="4" max="4" width="15.83203125" style="14" customWidth="1"/>
-    <col min="5" max="5" width="28.4140625" style="16" customWidth="1"/>
-    <col min="6" max="6" width="14.58203125" style="14" customWidth="1"/>
-    <col min="7" max="7" width="7.08203125" style="14" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="18" style="14" customWidth="1"/>
-    <col min="9" max="9" width="19.08203125" style="14" customWidth="1"/>
-    <col min="10" max="11" width="18.4140625" style="14" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="16.08203125" style="14" customWidth="1"/>
-    <col min="13" max="16384" width="8.83203125" style="14"/>
+    <col min="1" max="1" width="6.5" style="16" customWidth="1"/>
+    <col min="2" max="2" width="15.796875" style="15" customWidth="1"/>
+    <col min="3" max="3" width="29.69921875" style="15" customWidth="1"/>
+    <col min="4" max="4" width="15.796875" style="15" customWidth="1"/>
+    <col min="5" max="5" width="28.3984375" style="17" customWidth="1"/>
+    <col min="6" max="6" width="14.59765625" style="15" customWidth="1"/>
+    <col min="7" max="7" width="7.09765625" style="15" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="18" style="15" customWidth="1"/>
+    <col min="9" max="9" width="19.09765625" style="15" customWidth="1"/>
+    <col min="10" max="11" width="18.3984375" style="15" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="16.09765625" style="15" customWidth="1"/>
+    <col min="13" max="16384" width="8.796875" style="15"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" ht="15.65" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:12" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1185,13 +1193,13 @@
       <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="13" t="s">
+      <c r="D1" s="14" t="s">
         <v>32</v>
       </c>
-      <c r="E1" s="13" t="s">
+      <c r="E1" s="14" t="s">
         <v>33</v>
       </c>
-      <c r="F1" s="13" t="s">
+      <c r="F1" s="14" t="s">
         <v>37</v>
       </c>
       <c r="G1" s="2" t="s">
@@ -1206,280 +1214,254 @@
       <c r="J1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="K1" s="2" t="s">
+      <c r="K1" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="L1" s="4" t="s">
+      <c r="L1" s="5" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="2" spans="1:12" ht="46.5" x14ac:dyDescent="0.35">
-      <c r="A2" s="5">
+    <row r="2" spans="1:12" ht="30" x14ac:dyDescent="0.3">
+      <c r="A2" s="6">
         <v>1</v>
       </c>
-      <c r="B2" s="6" t="s">
+      <c r="B2" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="C2" s="6" t="s">
+      <c r="C2" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="D2" s="13"/>
-      <c r="E2" s="13"/>
-      <c r="F2" s="13"/>
-      <c r="G2" s="6">
+      <c r="D2" s="14"/>
+      <c r="E2" s="14"/>
+      <c r="F2" s="14"/>
+      <c r="G2" s="7">
         <v>2026</v>
       </c>
-      <c r="H2" s="7">
+      <c r="H2" s="8">
         <v>12552889759</v>
       </c>
-      <c r="I2" s="6" t="s">
+      <c r="I2" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="J2" s="6" t="s">
+      <c r="J2" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="K2" s="7">
-        <v>10000000000</v>
-      </c>
-      <c r="L2" s="7">
-        <v>10000000000</v>
-      </c>
+      <c r="K2" s="8"/>
+      <c r="L2" s="8"/>
     </row>
-    <row r="3" spans="1:12" ht="62" x14ac:dyDescent="0.35">
-      <c r="A3" s="5">
+    <row r="3" spans="1:12" ht="60" x14ac:dyDescent="0.3">
+      <c r="A3" s="6">
         <v>2</v>
       </c>
-      <c r="B3" s="6" t="s">
+      <c r="B3" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="C3" s="6" t="s">
+      <c r="C3" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="D3" s="12" t="s">
+      <c r="D3" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="E3" s="12"/>
-      <c r="F3" s="12"/>
-      <c r="G3" s="6">
+      <c r="E3" s="13"/>
+      <c r="F3" s="13"/>
+      <c r="G3" s="7">
         <v>2026</v>
       </c>
-      <c r="H3" s="7">
+      <c r="H3" s="8">
         <v>13650367159</v>
       </c>
-      <c r="I3" s="6" t="s">
+      <c r="I3" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="J3" s="6" t="s">
+      <c r="J3" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="K3" s="7">
+      <c r="K3" s="8">
         <v>1347233815</v>
       </c>
-      <c r="L3" s="7">
-        <v>1347233815</v>
-      </c>
+      <c r="L3" s="8"/>
     </row>
-    <row r="4" spans="1:12" ht="46.5" x14ac:dyDescent="0.35">
-      <c r="A4" s="5">
+    <row r="4" spans="1:12" ht="46.8" x14ac:dyDescent="0.3">
+      <c r="A4" s="6">
         <v>3</v>
       </c>
-      <c r="B4" s="6" t="s">
+      <c r="B4" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="C4" s="6" t="s">
+      <c r="C4" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="D4" s="12" t="s">
+      <c r="D4" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="E4" s="12" t="s">
+      <c r="E4" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="F4" s="12" t="s">
+      <c r="F4" s="13" t="s">
         <v>38</v>
       </c>
-      <c r="G4" s="6">
+      <c r="G4" s="7">
         <v>2026</v>
       </c>
-      <c r="H4" s="7">
+      <c r="H4" s="8">
         <v>3765771568</v>
       </c>
-      <c r="I4" s="6" t="s">
+      <c r="I4" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="J4" s="6" t="s">
+      <c r="J4" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="K4" s="7">
-        <v>3000000000</v>
-      </c>
-      <c r="L4" s="7">
-        <v>3000000000</v>
-      </c>
+      <c r="K4" s="8"/>
+      <c r="L4" s="8"/>
     </row>
-    <row r="5" spans="1:12" ht="46.5" x14ac:dyDescent="0.35">
-      <c r="A5" s="5">
+    <row r="5" spans="1:12" ht="45" x14ac:dyDescent="0.3">
+      <c r="A5" s="6">
         <v>4</v>
       </c>
-      <c r="B5" s="6" t="s">
+      <c r="B5" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="C5" s="6" t="s">
+      <c r="C5" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="D5" s="12"/>
-      <c r="E5" s="12"/>
-      <c r="F5" s="12"/>
-      <c r="G5" s="6">
+      <c r="D5" s="13"/>
+      <c r="E5" s="18"/>
+      <c r="F5" s="18"/>
+      <c r="G5" s="7">
         <v>2026</v>
       </c>
-      <c r="H5" s="7">
+      <c r="H5" s="8">
         <v>1590994000</v>
       </c>
-      <c r="I5" s="6" t="s">
+      <c r="I5" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="J5" s="6" t="s">
+      <c r="J5" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="K5" s="7">
-        <v>1000000000</v>
-      </c>
-      <c r="L5" s="7">
-        <v>1000000000</v>
-      </c>
+      <c r="K5" s="8"/>
+      <c r="L5" s="8"/>
     </row>
-    <row r="6" spans="1:12" ht="31" x14ac:dyDescent="0.35">
-      <c r="A6" s="5">
+    <row r="6" spans="1:12" ht="30" x14ac:dyDescent="0.3">
+      <c r="A6" s="6">
         <v>5</v>
       </c>
-      <c r="B6" s="6" t="s">
+      <c r="B6" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="C6" s="6" t="s">
+      <c r="C6" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="D6" s="12" t="s">
+      <c r="D6" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="E6" s="12"/>
-      <c r="F6" s="12"/>
-      <c r="G6" s="6">
+      <c r="E6" s="13"/>
+      <c r="F6" s="13"/>
+      <c r="G6" s="7">
         <v>2026</v>
       </c>
-      <c r="H6" s="7">
+      <c r="H6" s="8">
         <v>526699800</v>
       </c>
-      <c r="I6" s="6" t="s">
+      <c r="I6" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="J6" s="6" t="s">
+      <c r="J6" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="K6" s="7">
-        <v>500000000</v>
-      </c>
-      <c r="L6" s="7">
-        <v>500000000</v>
-      </c>
+      <c r="K6" s="8"/>
+      <c r="L6" s="8"/>
     </row>
-    <row r="7" spans="1:12" ht="46.5" x14ac:dyDescent="0.35">
-      <c r="A7" s="5">
+    <row r="7" spans="1:12" ht="46.8" x14ac:dyDescent="0.3">
+      <c r="A7" s="6">
         <v>6</v>
       </c>
-      <c r="B7" s="6" t="s">
+      <c r="B7" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="C7" s="6" t="s">
+      <c r="C7" s="7" t="s">
         <v>25</v>
       </c>
-      <c r="D7" s="12" t="s">
+      <c r="D7" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="E7" s="12" t="s">
+      <c r="E7" s="13" t="s">
         <v>36</v>
       </c>
-      <c r="F7" s="12" t="s">
+      <c r="F7" s="13" t="s">
         <v>38</v>
       </c>
-      <c r="G7" s="6">
+      <c r="G7" s="7">
         <v>2026</v>
       </c>
-      <c r="H7" s="7">
+      <c r="H7" s="8">
         <v>13236612376</v>
       </c>
-      <c r="I7" s="6" t="s">
+      <c r="I7" s="7" t="s">
         <v>26</v>
       </c>
-      <c r="J7" s="6" t="s">
+      <c r="J7" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="K7" s="7">
-        <v>5000000000</v>
-      </c>
-      <c r="L7" s="7">
-        <v>5000000000</v>
-      </c>
+      <c r="K7" s="8"/>
+      <c r="L7" s="8"/>
     </row>
-    <row r="8" spans="1:12" ht="46.5" x14ac:dyDescent="0.35">
-      <c r="A8" s="5">
+    <row r="8" spans="1:12" ht="45" x14ac:dyDescent="0.3">
+      <c r="A8" s="6">
         <v>7</v>
       </c>
-      <c r="B8" s="6" t="s">
+      <c r="B8" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="C8" s="6" t="s">
+      <c r="C8" s="7" t="s">
         <v>28</v>
       </c>
-      <c r="D8" s="12"/>
-      <c r="E8" s="12" t="s">
+      <c r="D8" s="13"/>
+      <c r="E8" s="18" t="s">
         <v>28</v>
       </c>
-      <c r="F8" s="12" t="s">
+      <c r="F8" s="18" t="s">
         <v>39</v>
       </c>
-      <c r="G8" s="6">
+      <c r="G8" s="7">
         <v>2026</v>
       </c>
-      <c r="H8" s="7">
+      <c r="H8" s="8">
         <v>5780025934</v>
       </c>
-      <c r="I8" s="6" t="s">
+      <c r="I8" s="7" t="s">
         <v>26</v>
       </c>
-      <c r="J8" s="6" t="s">
+      <c r="J8" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="K8" s="7">
-        <v>5000000000</v>
-      </c>
-      <c r="L8" s="7">
-        <v>5000000000</v>
-      </c>
+      <c r="K8" s="8"/>
+      <c r="L8" s="8"/>
     </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A9" s="8"/>
-      <c r="B9" s="9"/>
-      <c r="C9" s="10" t="s">
+    <row r="9" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A9" s="9"/>
+      <c r="B9" s="10"/>
+      <c r="C9" s="11" t="s">
         <v>29</v>
       </c>
-      <c r="D9" s="12"/>
-      <c r="E9" s="17"/>
-      <c r="F9" s="17"/>
-      <c r="G9" s="9"/>
-      <c r="H9" s="11">
+      <c r="D9" s="13"/>
+      <c r="E9" s="19"/>
+      <c r="F9" s="19"/>
+      <c r="G9" s="10"/>
+      <c r="H9" s="12">
         <f>SUM(H2:H8)</f>
         <v>51103360596</v>
       </c>
-      <c r="I9" s="9"/>
-      <c r="J9" s="9"/>
-      <c r="K9" s="11">
+      <c r="I9" s="10"/>
+      <c r="J9" s="10"/>
+      <c r="K9" s="12">
         <f t="shared" ref="K9:L9" si="0">SUM(K2:K8)</f>
-        <v>25847233815</v>
-      </c>
-      <c r="L9" s="11">
+        <v>1347233815</v>
+      </c>
+      <c r="L9" s="12">
         <f t="shared" si="0"/>
-        <v>25847233815</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/Tong Hop.xlsx
+++ b/Tong Hop.xlsx
@@ -2,15 +2,15 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
-  <workbookPr defaultThemeVersion="202300"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\1. TCKT_PCVT\4. Công nghệ AI\Các báo cáo\SCL\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\DATA\DATA_SCL\BC_SCL\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8979B0D0-F6FD-4BDE-AB98-75FB369C7EBB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{465B223C-0903-4C71-AC11-C902D96ACEE2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{EA8CD95B-BEDE-4E99-A9CD-4372C7F6DBD0}"/>
+    <workbookView xWindow="1100" yWindow="1100" windowWidth="21600" windowHeight="12710" xr2:uid="{EA8CD95B-BEDE-4E99-A9CD-4372C7F6DBD0}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -27,8 +27,6 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
     <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
@@ -39,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="38">
   <si>
     <t>STT</t>
   </si>
@@ -98,9 +96,6 @@
     <t>Đại tu công trình xây dựng dân dụng</t>
   </si>
   <si>
-    <t>Lập PAKT-Tổng dự toán</t>
-  </si>
-  <si>
     <t>VTAD2608001</t>
   </si>
   <si>
@@ -108,9 +103,6 @@
   </si>
   <si>
     <t>Đại tu công xa</t>
-  </si>
-  <si>
-    <t>Lập kế hoạch đấu thầu</t>
   </si>
   <si>
     <t>VTAD2610001</t>
@@ -166,8 +158,8 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="2">
-    <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="169" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="164" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="165" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;??_-;_-@_-"/>
   </numFmts>
   <fonts count="8" x14ac:knownFonts="1">
     <font>
@@ -325,10 +317,10 @@
   </borders>
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
@@ -339,10 +331,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -351,7 +340,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="169" fontId="2" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -363,7 +352,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="169" fontId="3" fillId="0" borderId="7" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="3" fillId="0" borderId="7" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -381,10 +370,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -395,28 +381,12 @@
   </cellStyles>
   <dxfs count="17">
     <dxf>
-      <alignment vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top/>
-        <bottom/>
-      </border>
-    </dxf>
-    <dxf>
       <font>
         <color rgb="FF1F1F1F"/>
         <name val="Arial"/>
         <family val="2"/>
       </font>
-      <numFmt numFmtId="169" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;??_-;_-@_-"/>
+      <numFmt numFmtId="165" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;??_-;_-@_-"/>
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="1"/>
       <border diagonalUp="0" diagonalDown="0" outline="0">
         <left style="thin">
@@ -439,7 +409,7 @@
         <name val="Arial"/>
         <family val="2"/>
       </font>
-      <numFmt numFmtId="169" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;??_-;_-@_-"/>
+      <numFmt numFmtId="165" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;??_-;_-@_-"/>
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="1"/>
       <border diagonalUp="0" diagonalDown="0" outline="0">
         <left style="thin">
@@ -539,7 +509,7 @@
         <family val="2"/>
         <scheme val="none"/>
       </font>
-      <numFmt numFmtId="169" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;??_-;_-@_-"/>
+      <numFmt numFmtId="165" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;??_-;_-@_-"/>
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="1"/>
       <border diagonalUp="0" diagonalDown="0" outline="0">
         <left style="thin">
@@ -793,6 +763,25 @@
       </border>
     </dxf>
     <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0"/>
+    </dxf>
+    <dxf>
       <border>
         <bottom style="thin">
           <color indexed="64"/>
@@ -800,19 +789,16 @@
       </border>
     </dxf>
     <dxf>
-      <border diagonalUp="0" diagonalDown="0">
+      <alignment vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
         <left style="thin">
           <color indexed="64"/>
         </left>
         <right style="thin">
           <color indexed="64"/>
         </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
+        <top/>
+        <bottom/>
       </border>
     </dxf>
   </dxfs>
@@ -829,21 +815,21 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{F1AB6DDC-BA93-481E-BD2B-9DF8058E8584}" name="Table1" displayName="Table1" ref="A1:L9" totalsRowShown="0" headerRowDxfId="1" dataDxfId="0" headerRowBorderDxfId="15" tableBorderDxfId="16" totalsRowBorderDxfId="14">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{F1AB6DDC-BA93-481E-BD2B-9DF8058E8584}" name="Table1" displayName="Table1" ref="A1:L9" totalsRowShown="0" headerRowDxfId="16" dataDxfId="14" headerRowBorderDxfId="15" tableBorderDxfId="13" totalsRowBorderDxfId="12">
   <autoFilter ref="A1:L9" xr:uid="{F1AB6DDC-BA93-481E-BD2B-9DF8058E8584}"/>
   <tableColumns count="12">
-    <tableColumn id="1" xr3:uid="{DAC04565-69BC-4CDF-9E0A-EC1119831221}" name="STT" dataDxfId="13"/>
-    <tableColumn id="2" xr3:uid="{D6161F9A-87AA-431B-80BE-36A93E2AFC54}" name="Mã công trình" dataDxfId="12"/>
-    <tableColumn id="3" xr3:uid="{B6921986-DEFB-4044-8199-A3891359D0D8}" name="Tên công trình" dataDxfId="11"/>
-    <tableColumn id="10" xr3:uid="{1BF7E3F8-25B1-4DF4-B523-310B52CF464E}" name="Số QĐ phê duyệt danh mục" dataDxfId="10" dataCellStyle="Normal 2"/>
-    <tableColumn id="11" xr3:uid="{3AE98590-A534-40D4-A68D-3A7A411590AD}" name="Nội dung chính sữa chữa " dataDxfId="9" dataCellStyle="Normal 2"/>
-    <tableColumn id="12" xr3:uid="{465F0A31-3F91-4822-BA14-948A18D11083}" name="Tiến độ thực hiện theo kế hoạch" dataDxfId="8" dataCellStyle="Normal 2"/>
-    <tableColumn id="4" xr3:uid="{CA856511-17A6-4630-B6ED-3630EBCB18AF}" name="Năm" dataDxfId="7"/>
-    <tableColumn id="5" xr3:uid="{8E900E18-E817-403C-991D-0FB1E7E5763A}" name="Giá trị khái toán" dataDxfId="6" dataCellStyle="Comma"/>
-    <tableColumn id="6" xr3:uid="{F1B544CF-5D4E-4E6C-834E-112E2E2B9814}" name="Tên hạng mục" dataDxfId="5"/>
-    <tableColumn id="7" xr3:uid="{AEFAD23C-45D2-400E-AB7E-19B2CD7F4803}" name="Trạng thái" dataDxfId="4"/>
-    <tableColumn id="8" xr3:uid="{2675D14E-65F9-45FF-90BF-967C376D3844}" name="Giá trị thực hiện" dataDxfId="3" dataCellStyle="Comma"/>
-    <tableColumn id="9" xr3:uid="{695670EC-1745-48D9-9A74-4408C2464719}" name="Giá trị quyết toán" dataDxfId="2" dataCellStyle="Comma"/>
+    <tableColumn id="1" xr3:uid="{DAC04565-69BC-4CDF-9E0A-EC1119831221}" name="STT" dataDxfId="11"/>
+    <tableColumn id="2" xr3:uid="{D6161F9A-87AA-431B-80BE-36A93E2AFC54}" name="Mã công trình" dataDxfId="10"/>
+    <tableColumn id="3" xr3:uid="{B6921986-DEFB-4044-8199-A3891359D0D8}" name="Tên công trình" dataDxfId="9"/>
+    <tableColumn id="10" xr3:uid="{1BF7E3F8-25B1-4DF4-B523-310B52CF464E}" name="Số QĐ phê duyệt danh mục" dataDxfId="8" dataCellStyle="Normal 2"/>
+    <tableColumn id="11" xr3:uid="{3AE98590-A534-40D4-A68D-3A7A411590AD}" name="Nội dung chính sữa chữa " dataDxfId="7" dataCellStyle="Normal 2"/>
+    <tableColumn id="12" xr3:uid="{465F0A31-3F91-4822-BA14-948A18D11083}" name="Tiến độ thực hiện theo kế hoạch" dataDxfId="6" dataCellStyle="Normal 2"/>
+    <tableColumn id="4" xr3:uid="{CA856511-17A6-4630-B6ED-3630EBCB18AF}" name="Năm" dataDxfId="5"/>
+    <tableColumn id="5" xr3:uid="{8E900E18-E817-403C-991D-0FB1E7E5763A}" name="Giá trị khái toán" dataDxfId="4" dataCellStyle="Comma"/>
+    <tableColumn id="6" xr3:uid="{F1B544CF-5D4E-4E6C-834E-112E2E2B9814}" name="Tên hạng mục" dataDxfId="3"/>
+    <tableColumn id="7" xr3:uid="{AEFAD23C-45D2-400E-AB7E-19B2CD7F4803}" name="Trạng thái" dataDxfId="2"/>
+    <tableColumn id="8" xr3:uid="{2675D14E-65F9-45FF-90BF-967C376D3844}" name="Giá trị thực hiện" dataDxfId="1" dataCellStyle="Comma"/>
+    <tableColumn id="9" xr3:uid="{695670EC-1745-48D9-9A74-4408C2464719}" name="Giá trị quyết toán" dataDxfId="0" dataCellStyle="Comma"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1167,23 +1153,23 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B84B92FB-9617-4ECC-974D-88D4E382CA3F}">
   <dimension ref="A1:L9"/>
-  <sheetFormatPr defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="8.83203125" defaultRowHeight="15.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="6.5" style="16" customWidth="1"/>
-    <col min="2" max="2" width="15.796875" style="15" customWidth="1"/>
-    <col min="3" max="3" width="29.69921875" style="15" customWidth="1"/>
-    <col min="4" max="4" width="15.796875" style="15" customWidth="1"/>
-    <col min="5" max="5" width="28.3984375" style="17" customWidth="1"/>
-    <col min="6" max="6" width="14.59765625" style="15" customWidth="1"/>
-    <col min="7" max="7" width="7.09765625" style="15" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="18" style="15" customWidth="1"/>
-    <col min="9" max="9" width="19.09765625" style="15" customWidth="1"/>
-    <col min="10" max="11" width="18.3984375" style="15" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="16.09765625" style="15" customWidth="1"/>
-    <col min="13" max="16384" width="8.796875" style="15"/>
+    <col min="1" max="1" width="6.5" style="15" customWidth="1"/>
+    <col min="2" max="2" width="15.83203125" style="14" customWidth="1"/>
+    <col min="3" max="3" width="29.6640625" style="14" customWidth="1"/>
+    <col min="4" max="4" width="15.83203125" style="14" customWidth="1"/>
+    <col min="5" max="5" width="28.4140625" style="16" customWidth="1"/>
+    <col min="6" max="6" width="14.58203125" style="14" customWidth="1"/>
+    <col min="7" max="7" width="7.08203125" style="14" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="18" style="14" customWidth="1"/>
+    <col min="9" max="9" width="19.08203125" style="14" customWidth="1"/>
+    <col min="10" max="11" width="18.4140625" style="14" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="16.08203125" style="14" customWidth="1"/>
+    <col min="13" max="16384" width="8.83203125" style="14"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:12" ht="15.65" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1193,14 +1179,14 @@
       <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="14" t="s">
-        <v>32</v>
-      </c>
-      <c r="E1" s="14" t="s">
-        <v>33</v>
-      </c>
-      <c r="F1" s="14" t="s">
-        <v>37</v>
+      <c r="D1" s="13" t="s">
+        <v>30</v>
+      </c>
+      <c r="E1" s="13" t="s">
+        <v>31</v>
+      </c>
+      <c r="F1" s="13" t="s">
+        <v>35</v>
       </c>
       <c r="G1" s="2" t="s">
         <v>3</v>
@@ -1214,254 +1200,280 @@
       <c r="J1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="K1" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="L1" s="5" t="s">
-        <v>31</v>
+      <c r="K1" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="L1" s="4" t="s">
+        <v>29</v>
       </c>
     </row>
-    <row r="2" spans="1:12" ht="30" x14ac:dyDescent="0.3">
-      <c r="A2" s="6">
+    <row r="2" spans="1:12" ht="46.5" x14ac:dyDescent="0.35">
+      <c r="A2" s="5">
         <v>1</v>
       </c>
-      <c r="B2" s="7" t="s">
+      <c r="B2" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="C2" s="7" t="s">
+      <c r="C2" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="D2" s="14"/>
-      <c r="E2" s="14"/>
-      <c r="F2" s="14"/>
-      <c r="G2" s="7">
+      <c r="D2" s="13"/>
+      <c r="E2" s="13"/>
+      <c r="F2" s="13"/>
+      <c r="G2" s="6">
         <v>2026</v>
       </c>
-      <c r="H2" s="8">
+      <c r="H2" s="7">
         <v>12552889759</v>
       </c>
-      <c r="I2" s="7" t="s">
+      <c r="I2" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="J2" s="7" t="s">
+      <c r="J2" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="K2" s="8"/>
-      <c r="L2" s="8"/>
+      <c r="K2" s="7">
+        <v>10000000000</v>
+      </c>
+      <c r="L2" s="7">
+        <v>10000000000</v>
+      </c>
     </row>
-    <row r="3" spans="1:12" ht="60" x14ac:dyDescent="0.3">
-      <c r="A3" s="6">
+    <row r="3" spans="1:12" ht="62" x14ac:dyDescent="0.35">
+      <c r="A3" s="5">
         <v>2</v>
       </c>
-      <c r="B3" s="7" t="s">
+      <c r="B3" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="C3" s="7" t="s">
+      <c r="C3" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="D3" s="13" t="s">
+      <c r="D3" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="E3" s="12"/>
+      <c r="F3" s="12"/>
+      <c r="G3" s="6">
+        <v>2026</v>
+      </c>
+      <c r="H3" s="7">
+        <v>13650367159</v>
+      </c>
+      <c r="I3" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="J3" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="K3" s="7">
+        <v>1347233815</v>
+      </c>
+      <c r="L3" s="7">
+        <v>1347233815</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" ht="46.5" x14ac:dyDescent="0.35">
+      <c r="A4" s="5">
+        <v>3</v>
+      </c>
+      <c r="B4" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="C4" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="D4" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="E4" s="12" t="s">
+        <v>33</v>
+      </c>
+      <c r="F4" s="12" t="s">
+        <v>36</v>
+      </c>
+      <c r="G4" s="6">
+        <v>2026</v>
+      </c>
+      <c r="H4" s="7">
+        <v>3765771568</v>
+      </c>
+      <c r="I4" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="J4" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="K4" s="7">
+        <v>3000000000</v>
+      </c>
+      <c r="L4" s="7">
+        <v>3000000000</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" ht="46.5" x14ac:dyDescent="0.35">
+      <c r="A5" s="5">
+        <v>4</v>
+      </c>
+      <c r="B5" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="C5" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="D5" s="12"/>
+      <c r="E5" s="12"/>
+      <c r="F5" s="12"/>
+      <c r="G5" s="6">
+        <v>2026</v>
+      </c>
+      <c r="H5" s="7">
+        <v>1590994000</v>
+      </c>
+      <c r="I5" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="J5" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="K5" s="7">
+        <v>1000000000</v>
+      </c>
+      <c r="L5" s="7">
+        <v>1000000000</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" ht="31" x14ac:dyDescent="0.35">
+      <c r="A6" s="5">
+        <v>5</v>
+      </c>
+      <c r="B6" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="C6" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="D6" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="E6" s="12"/>
+      <c r="F6" s="12"/>
+      <c r="G6" s="6">
+        <v>2026</v>
+      </c>
+      <c r="H6" s="7">
+        <v>526699800</v>
+      </c>
+      <c r="I6" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="J6" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="K6" s="7">
+        <v>500000000</v>
+      </c>
+      <c r="L6" s="7">
+        <v>500000000</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" ht="46.5" x14ac:dyDescent="0.35">
+      <c r="A7" s="5">
+        <v>6</v>
+      </c>
+      <c r="B7" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="C7" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="D7" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="E7" s="12" t="s">
         <v>34</v>
       </c>
-      <c r="E3" s="13"/>
-      <c r="F3" s="13"/>
-      <c r="G3" s="7">
+      <c r="F7" s="12" t="s">
+        <v>36</v>
+      </c>
+      <c r="G7" s="6">
         <v>2026</v>
       </c>
-      <c r="H3" s="8">
-        <v>13650367159</v>
-      </c>
-      <c r="I3" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="J3" s="7" t="s">
+      <c r="H7" s="7">
+        <v>13236612376</v>
+      </c>
+      <c r="I7" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="J7" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="K3" s="8">
-        <v>1347233815</v>
-      </c>
-      <c r="L3" s="8"/>
+      <c r="K7" s="7">
+        <v>10000000000</v>
+      </c>
+      <c r="L7" s="7">
+        <v>10000000000</v>
+      </c>
     </row>
-    <row r="4" spans="1:12" ht="46.8" x14ac:dyDescent="0.3">
-      <c r="A4" s="6">
-        <v>3</v>
-      </c>
-      <c r="B4" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="C4" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="D4" s="13" t="s">
-        <v>34</v>
-      </c>
-      <c r="E4" s="13" t="s">
-        <v>35</v>
-      </c>
-      <c r="F4" s="13" t="s">
-        <v>38</v>
-      </c>
-      <c r="G4" s="7">
+    <row r="8" spans="1:12" ht="46.5" x14ac:dyDescent="0.35">
+      <c r="A8" s="5">
+        <v>7</v>
+      </c>
+      <c r="B8" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="C8" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="D8" s="12"/>
+      <c r="E8" s="12" t="s">
+        <v>26</v>
+      </c>
+      <c r="F8" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="G8" s="6">
         <v>2026</v>
       </c>
-      <c r="H4" s="8">
-        <v>3765771568</v>
-      </c>
-      <c r="I4" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="J4" s="7" t="s">
+      <c r="H8" s="7">
+        <v>5780025934</v>
+      </c>
+      <c r="I8" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="J8" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="K4" s="8"/>
-      <c r="L4" s="8"/>
+      <c r="K8" s="7">
+        <v>5000000000</v>
+      </c>
+      <c r="L8" s="7">
+        <v>5000000000</v>
+      </c>
     </row>
-    <row r="5" spans="1:12" ht="45" x14ac:dyDescent="0.3">
-      <c r="A5" s="6">
-        <v>4</v>
-      </c>
-      <c r="B5" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="C5" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="D5" s="13"/>
-      <c r="E5" s="18"/>
-      <c r="F5" s="18"/>
-      <c r="G5" s="7">
-        <v>2026</v>
-      </c>
-      <c r="H5" s="8">
-        <v>1590994000</v>
-      </c>
-      <c r="I5" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="J5" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="K5" s="8"/>
-      <c r="L5" s="8"/>
-    </row>
-    <row r="6" spans="1:12" ht="30" x14ac:dyDescent="0.3">
-      <c r="A6" s="6">
-        <v>5</v>
-      </c>
-      <c r="B6" s="7" t="s">
-        <v>20</v>
-      </c>
-      <c r="C6" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="D6" s="13" t="s">
-        <v>34</v>
-      </c>
-      <c r="E6" s="13"/>
-      <c r="F6" s="13"/>
-      <c r="G6" s="7">
-        <v>2026</v>
-      </c>
-      <c r="H6" s="8">
-        <v>526699800</v>
-      </c>
-      <c r="I6" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="J6" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="K6" s="8"/>
-      <c r="L6" s="8"/>
-    </row>
-    <row r="7" spans="1:12" ht="46.8" x14ac:dyDescent="0.3">
-      <c r="A7" s="6">
-        <v>6</v>
-      </c>
-      <c r="B7" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="C7" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="D7" s="13" t="s">
-        <v>34</v>
-      </c>
-      <c r="E7" s="13" t="s">
-        <v>36</v>
-      </c>
-      <c r="F7" s="13" t="s">
-        <v>38</v>
-      </c>
-      <c r="G7" s="7">
-        <v>2026</v>
-      </c>
-      <c r="H7" s="8">
-        <v>13236612376</v>
-      </c>
-      <c r="I7" s="7" t="s">
-        <v>26</v>
-      </c>
-      <c r="J7" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="K7" s="8"/>
-      <c r="L7" s="8"/>
-    </row>
-    <row r="8" spans="1:12" ht="45" x14ac:dyDescent="0.3">
-      <c r="A8" s="6">
-        <v>7</v>
-      </c>
-      <c r="B8" s="7" t="s">
+    <row r="9" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A9" s="8"/>
+      <c r="B9" s="9"/>
+      <c r="C9" s="10" t="s">
         <v>27</v>
       </c>
-      <c r="C8" s="7" t="s">
-        <v>28</v>
-      </c>
-      <c r="D8" s="13"/>
-      <c r="E8" s="18" t="s">
-        <v>28</v>
-      </c>
-      <c r="F8" s="18" t="s">
-        <v>39</v>
-      </c>
-      <c r="G8" s="7">
-        <v>2026</v>
-      </c>
-      <c r="H8" s="8">
-        <v>5780025934</v>
-      </c>
-      <c r="I8" s="7" t="s">
-        <v>26</v>
-      </c>
-      <c r="J8" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="K8" s="8"/>
-      <c r="L8" s="8"/>
-    </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A9" s="9"/>
-      <c r="B9" s="10"/>
-      <c r="C9" s="11" t="s">
-        <v>29</v>
-      </c>
-      <c r="D9" s="13"/>
-      <c r="E9" s="19"/>
-      <c r="F9" s="19"/>
-      <c r="G9" s="10"/>
-      <c r="H9" s="12">
+      <c r="D9" s="12"/>
+      <c r="E9" s="17"/>
+      <c r="F9" s="17"/>
+      <c r="G9" s="9"/>
+      <c r="H9" s="11">
         <f>SUM(H2:H8)</f>
         <v>51103360596</v>
       </c>
-      <c r="I9" s="10"/>
-      <c r="J9" s="10"/>
-      <c r="K9" s="12">
+      <c r="I9" s="9"/>
+      <c r="J9" s="9"/>
+      <c r="K9" s="11">
         <f t="shared" ref="K9:L9" si="0">SUM(K2:K8)</f>
-        <v>1347233815</v>
-      </c>
-      <c r="L9" s="12">
+        <v>30847233815</v>
+      </c>
+      <c r="L9" s="11">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>30847233815</v>
       </c>
     </row>
   </sheetData>

--- a/Tong Hop.xlsx
+++ b/Tong Hop.xlsx
@@ -2,15 +2,15 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
-  <workbookPr/>
+  <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\DATA\DATA_SCL\BC_SCL\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\1. TCKT_PCVT\4. Công nghệ AI\Các báo cáo\SCL\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{465B223C-0903-4C71-AC11-C902D96ACEE2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8979B0D0-F6FD-4BDE-AB98-75FB369C7EBB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1100" yWindow="1100" windowWidth="21600" windowHeight="12710" xr2:uid="{EA8CD95B-BEDE-4E99-A9CD-4372C7F6DBD0}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{EA8CD95B-BEDE-4E99-A9CD-4372C7F6DBD0}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -27,6 +27,8 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
     <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
@@ -37,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="38">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="40">
   <si>
     <t>STT</t>
   </si>
@@ -96,6 +98,9 @@
     <t>Đại tu công trình xây dựng dân dụng</t>
   </si>
   <si>
+    <t>Lập PAKT-Tổng dự toán</t>
+  </si>
+  <si>
     <t>VTAD2608001</t>
   </si>
   <si>
@@ -103,6 +108,9 @@
   </si>
   <si>
     <t>Đại tu công xa</t>
+  </si>
+  <si>
+    <t>Lập kế hoạch đấu thầu</t>
   </si>
   <si>
     <t>VTAD2610001</t>
@@ -158,8 +166,8 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="2">
-    <numFmt numFmtId="164" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="165" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="169" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;??_-;_-@_-"/>
   </numFmts>
   <fonts count="8" x14ac:knownFonts="1">
     <font>
@@ -317,10 +325,10 @@
   </borders>
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
@@ -331,7 +339,10 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -340,7 +351,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="169" fontId="2" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -352,7 +363,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="165" fontId="3" fillId="0" borderId="7" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="169" fontId="3" fillId="0" borderId="7" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -370,7 +381,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -381,12 +395,28 @@
   </cellStyles>
   <dxfs count="17">
     <dxf>
+      <alignment vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top/>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
       <font>
         <color rgb="FF1F1F1F"/>
         <name val="Arial"/>
         <family val="2"/>
       </font>
-      <numFmt numFmtId="165" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;??_-;_-@_-"/>
+      <numFmt numFmtId="169" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;??_-;_-@_-"/>
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="1"/>
       <border diagonalUp="0" diagonalDown="0" outline="0">
         <left style="thin">
@@ -409,7 +439,7 @@
         <name val="Arial"/>
         <family val="2"/>
       </font>
-      <numFmt numFmtId="165" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;??_-;_-@_-"/>
+      <numFmt numFmtId="169" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;??_-;_-@_-"/>
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="1"/>
       <border diagonalUp="0" diagonalDown="0" outline="0">
         <left style="thin">
@@ -509,7 +539,7 @@
         <family val="2"/>
         <scheme val="none"/>
       </font>
-      <numFmt numFmtId="165" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;??_-;_-@_-"/>
+      <numFmt numFmtId="169" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;??_-;_-@_-"/>
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="1"/>
       <border diagonalUp="0" diagonalDown="0" outline="0">
         <left style="thin">
@@ -763,6 +793,13 @@
       </border>
     </dxf>
     <dxf>
+      <border>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
       <border diagonalUp="0" diagonalDown="0">
         <left style="thin">
           <color indexed="64"/>
@@ -776,29 +813,6 @@
         <bottom style="thin">
           <color indexed="64"/>
         </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0"/>
-    </dxf>
-    <dxf>
-      <border>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top/>
-        <bottom/>
       </border>
     </dxf>
   </dxfs>
@@ -815,21 +829,21 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{F1AB6DDC-BA93-481E-BD2B-9DF8058E8584}" name="Table1" displayName="Table1" ref="A1:L9" totalsRowShown="0" headerRowDxfId="16" dataDxfId="14" headerRowBorderDxfId="15" tableBorderDxfId="13" totalsRowBorderDxfId="12">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{F1AB6DDC-BA93-481E-BD2B-9DF8058E8584}" name="Table1" displayName="Table1" ref="A1:L9" totalsRowShown="0" headerRowDxfId="1" dataDxfId="0" headerRowBorderDxfId="15" tableBorderDxfId="16" totalsRowBorderDxfId="14">
   <autoFilter ref="A1:L9" xr:uid="{F1AB6DDC-BA93-481E-BD2B-9DF8058E8584}"/>
   <tableColumns count="12">
-    <tableColumn id="1" xr3:uid="{DAC04565-69BC-4CDF-9E0A-EC1119831221}" name="STT" dataDxfId="11"/>
-    <tableColumn id="2" xr3:uid="{D6161F9A-87AA-431B-80BE-36A93E2AFC54}" name="Mã công trình" dataDxfId="10"/>
-    <tableColumn id="3" xr3:uid="{B6921986-DEFB-4044-8199-A3891359D0D8}" name="Tên công trình" dataDxfId="9"/>
-    <tableColumn id="10" xr3:uid="{1BF7E3F8-25B1-4DF4-B523-310B52CF464E}" name="Số QĐ phê duyệt danh mục" dataDxfId="8" dataCellStyle="Normal 2"/>
-    <tableColumn id="11" xr3:uid="{3AE98590-A534-40D4-A68D-3A7A411590AD}" name="Nội dung chính sữa chữa " dataDxfId="7" dataCellStyle="Normal 2"/>
-    <tableColumn id="12" xr3:uid="{465F0A31-3F91-4822-BA14-948A18D11083}" name="Tiến độ thực hiện theo kế hoạch" dataDxfId="6" dataCellStyle="Normal 2"/>
-    <tableColumn id="4" xr3:uid="{CA856511-17A6-4630-B6ED-3630EBCB18AF}" name="Năm" dataDxfId="5"/>
-    <tableColumn id="5" xr3:uid="{8E900E18-E817-403C-991D-0FB1E7E5763A}" name="Giá trị khái toán" dataDxfId="4" dataCellStyle="Comma"/>
-    <tableColumn id="6" xr3:uid="{F1B544CF-5D4E-4E6C-834E-112E2E2B9814}" name="Tên hạng mục" dataDxfId="3"/>
-    <tableColumn id="7" xr3:uid="{AEFAD23C-45D2-400E-AB7E-19B2CD7F4803}" name="Trạng thái" dataDxfId="2"/>
-    <tableColumn id="8" xr3:uid="{2675D14E-65F9-45FF-90BF-967C376D3844}" name="Giá trị thực hiện" dataDxfId="1" dataCellStyle="Comma"/>
-    <tableColumn id="9" xr3:uid="{695670EC-1745-48D9-9A74-4408C2464719}" name="Giá trị quyết toán" dataDxfId="0" dataCellStyle="Comma"/>
+    <tableColumn id="1" xr3:uid="{DAC04565-69BC-4CDF-9E0A-EC1119831221}" name="STT" dataDxfId="13"/>
+    <tableColumn id="2" xr3:uid="{D6161F9A-87AA-431B-80BE-36A93E2AFC54}" name="Mã công trình" dataDxfId="12"/>
+    <tableColumn id="3" xr3:uid="{B6921986-DEFB-4044-8199-A3891359D0D8}" name="Tên công trình" dataDxfId="11"/>
+    <tableColumn id="10" xr3:uid="{1BF7E3F8-25B1-4DF4-B523-310B52CF464E}" name="Số QĐ phê duyệt danh mục" dataDxfId="10" dataCellStyle="Normal 2"/>
+    <tableColumn id="11" xr3:uid="{3AE98590-A534-40D4-A68D-3A7A411590AD}" name="Nội dung chính sữa chữa " dataDxfId="9" dataCellStyle="Normal 2"/>
+    <tableColumn id="12" xr3:uid="{465F0A31-3F91-4822-BA14-948A18D11083}" name="Tiến độ thực hiện theo kế hoạch" dataDxfId="8" dataCellStyle="Normal 2"/>
+    <tableColumn id="4" xr3:uid="{CA856511-17A6-4630-B6ED-3630EBCB18AF}" name="Năm" dataDxfId="7"/>
+    <tableColumn id="5" xr3:uid="{8E900E18-E817-403C-991D-0FB1E7E5763A}" name="Giá trị khái toán" dataDxfId="6" dataCellStyle="Comma"/>
+    <tableColumn id="6" xr3:uid="{F1B544CF-5D4E-4E6C-834E-112E2E2B9814}" name="Tên hạng mục" dataDxfId="5"/>
+    <tableColumn id="7" xr3:uid="{AEFAD23C-45D2-400E-AB7E-19B2CD7F4803}" name="Trạng thái" dataDxfId="4"/>
+    <tableColumn id="8" xr3:uid="{2675D14E-65F9-45FF-90BF-967C376D3844}" name="Giá trị thực hiện" dataDxfId="3" dataCellStyle="Comma"/>
+    <tableColumn id="9" xr3:uid="{695670EC-1745-48D9-9A74-4408C2464719}" name="Giá trị quyết toán" dataDxfId="2" dataCellStyle="Comma"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1153,23 +1167,23 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B84B92FB-9617-4ECC-974D-88D4E382CA3F}">
   <dimension ref="A1:L9"/>
-  <sheetFormatPr defaultColWidth="8.83203125" defaultRowHeight="15.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="6.5" style="15" customWidth="1"/>
-    <col min="2" max="2" width="15.83203125" style="14" customWidth="1"/>
-    <col min="3" max="3" width="29.6640625" style="14" customWidth="1"/>
-    <col min="4" max="4" width="15.83203125" style="14" customWidth="1"/>
-    <col min="5" max="5" width="28.4140625" style="16" customWidth="1"/>
-    <col min="6" max="6" width="14.58203125" style="14" customWidth="1"/>
-    <col min="7" max="7" width="7.08203125" style="14" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="18" style="14" customWidth="1"/>
-    <col min="9" max="9" width="19.08203125" style="14" customWidth="1"/>
-    <col min="10" max="11" width="18.4140625" style="14" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="16.08203125" style="14" customWidth="1"/>
-    <col min="13" max="16384" width="8.83203125" style="14"/>
+    <col min="1" max="1" width="6.5" style="16" customWidth="1"/>
+    <col min="2" max="2" width="15.796875" style="15" customWidth="1"/>
+    <col min="3" max="3" width="29.69921875" style="15" customWidth="1"/>
+    <col min="4" max="4" width="15.796875" style="15" customWidth="1"/>
+    <col min="5" max="5" width="28.3984375" style="17" customWidth="1"/>
+    <col min="6" max="6" width="14.59765625" style="15" customWidth="1"/>
+    <col min="7" max="7" width="7.09765625" style="15" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="18" style="15" customWidth="1"/>
+    <col min="9" max="9" width="19.09765625" style="15" customWidth="1"/>
+    <col min="10" max="11" width="18.3984375" style="15" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="16.09765625" style="15" customWidth="1"/>
+    <col min="13" max="16384" width="8.796875" style="15"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" ht="15.65" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:12" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1179,14 +1193,14 @@
       <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="13" t="s">
-        <v>30</v>
-      </c>
-      <c r="E1" s="13" t="s">
-        <v>31</v>
-      </c>
-      <c r="F1" s="13" t="s">
-        <v>35</v>
+      <c r="D1" s="14" t="s">
+        <v>32</v>
+      </c>
+      <c r="E1" s="14" t="s">
+        <v>33</v>
+      </c>
+      <c r="F1" s="14" t="s">
+        <v>37</v>
       </c>
       <c r="G1" s="2" t="s">
         <v>3</v>
@@ -1200,280 +1214,254 @@
       <c r="J1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="K1" s="2" t="s">
+      <c r="K1" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="L1" s="5" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12" ht="30" x14ac:dyDescent="0.3">
+      <c r="A2" s="6">
+        <v>1</v>
+      </c>
+      <c r="B2" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C2" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="D2" s="14"/>
+      <c r="E2" s="14"/>
+      <c r="F2" s="14"/>
+      <c r="G2" s="7">
+        <v>2026</v>
+      </c>
+      <c r="H2" s="8">
+        <v>12552889759</v>
+      </c>
+      <c r="I2" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="J2" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="K2" s="8"/>
+      <c r="L2" s="8"/>
+    </row>
+    <row r="3" spans="1:12" ht="60" x14ac:dyDescent="0.3">
+      <c r="A3" s="6">
+        <v>2</v>
+      </c>
+      <c r="B3" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="C3" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="D3" s="13" t="s">
+        <v>34</v>
+      </c>
+      <c r="E3" s="13"/>
+      <c r="F3" s="13"/>
+      <c r="G3" s="7">
+        <v>2026</v>
+      </c>
+      <c r="H3" s="8">
+        <v>13650367159</v>
+      </c>
+      <c r="I3" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="J3" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="K3" s="8">
+        <v>1347233815</v>
+      </c>
+      <c r="L3" s="8"/>
+    </row>
+    <row r="4" spans="1:12" ht="46.8" x14ac:dyDescent="0.3">
+      <c r="A4" s="6">
+        <v>3</v>
+      </c>
+      <c r="B4" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="C4" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="D4" s="13" t="s">
+        <v>34</v>
+      </c>
+      <c r="E4" s="13" t="s">
+        <v>35</v>
+      </c>
+      <c r="F4" s="13" t="s">
+        <v>38</v>
+      </c>
+      <c r="G4" s="7">
+        <v>2026</v>
+      </c>
+      <c r="H4" s="8">
+        <v>3765771568</v>
+      </c>
+      <c r="I4" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="J4" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="K4" s="8"/>
+      <c r="L4" s="8"/>
+    </row>
+    <row r="5" spans="1:12" ht="45" x14ac:dyDescent="0.3">
+      <c r="A5" s="6">
+        <v>4</v>
+      </c>
+      <c r="B5" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="C5" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D5" s="13"/>
+      <c r="E5" s="18"/>
+      <c r="F5" s="18"/>
+      <c r="G5" s="7">
+        <v>2026</v>
+      </c>
+      <c r="H5" s="8">
+        <v>1590994000</v>
+      </c>
+      <c r="I5" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="J5" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="K5" s="8"/>
+      <c r="L5" s="8"/>
+    </row>
+    <row r="6" spans="1:12" ht="30" x14ac:dyDescent="0.3">
+      <c r="A6" s="6">
+        <v>5</v>
+      </c>
+      <c r="B6" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="C6" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="D6" s="13" t="s">
+        <v>34</v>
+      </c>
+      <c r="E6" s="13"/>
+      <c r="F6" s="13"/>
+      <c r="G6" s="7">
+        <v>2026</v>
+      </c>
+      <c r="H6" s="8">
+        <v>526699800</v>
+      </c>
+      <c r="I6" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="J6" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="K6" s="8"/>
+      <c r="L6" s="8"/>
+    </row>
+    <row r="7" spans="1:12" ht="46.8" x14ac:dyDescent="0.3">
+      <c r="A7" s="6">
+        <v>6</v>
+      </c>
+      <c r="B7" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="C7" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="D7" s="13" t="s">
+        <v>34</v>
+      </c>
+      <c r="E7" s="13" t="s">
+        <v>36</v>
+      </c>
+      <c r="F7" s="13" t="s">
+        <v>38</v>
+      </c>
+      <c r="G7" s="7">
+        <v>2026</v>
+      </c>
+      <c r="H7" s="8">
+        <v>13236612376</v>
+      </c>
+      <c r="I7" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="J7" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="K7" s="8"/>
+      <c r="L7" s="8"/>
+    </row>
+    <row r="8" spans="1:12" ht="45" x14ac:dyDescent="0.3">
+      <c r="A8" s="6">
+        <v>7</v>
+      </c>
+      <c r="B8" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="C8" s="7" t="s">
         <v>28</v>
       </c>
-      <c r="L1" s="4" t="s">
+      <c r="D8" s="13"/>
+      <c r="E8" s="18" t="s">
+        <v>28</v>
+      </c>
+      <c r="F8" s="18" t="s">
+        <v>39</v>
+      </c>
+      <c r="G8" s="7">
+        <v>2026</v>
+      </c>
+      <c r="H8" s="8">
+        <v>5780025934</v>
+      </c>
+      <c r="I8" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="J8" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="K8" s="8"/>
+      <c r="L8" s="8"/>
+    </row>
+    <row r="9" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A9" s="9"/>
+      <c r="B9" s="10"/>
+      <c r="C9" s="11" t="s">
         <v>29</v>
       </c>
-    </row>
-    <row r="2" spans="1:12" ht="46.5" x14ac:dyDescent="0.35">
-      <c r="A2" s="5">
-        <v>1</v>
-      </c>
-      <c r="B2" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="C2" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="D2" s="13"/>
-      <c r="E2" s="13"/>
-      <c r="F2" s="13"/>
-      <c r="G2" s="6">
-        <v>2026</v>
-      </c>
-      <c r="H2" s="7">
-        <v>12552889759</v>
-      </c>
-      <c r="I2" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="J2" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="K2" s="7">
-        <v>10000000000</v>
-      </c>
-      <c r="L2" s="7">
-        <v>10000000000</v>
-      </c>
-    </row>
-    <row r="3" spans="1:12" ht="62" x14ac:dyDescent="0.35">
-      <c r="A3" s="5">
-        <v>2</v>
-      </c>
-      <c r="B3" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C3" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="D3" s="12" t="s">
-        <v>32</v>
-      </c>
-      <c r="E3" s="12"/>
-      <c r="F3" s="12"/>
-      <c r="G3" s="6">
-        <v>2026</v>
-      </c>
-      <c r="H3" s="7">
-        <v>13650367159</v>
-      </c>
-      <c r="I3" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="J3" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="K3" s="7">
-        <v>1347233815</v>
-      </c>
-      <c r="L3" s="7">
-        <v>1347233815</v>
-      </c>
-    </row>
-    <row r="4" spans="1:12" ht="46.5" x14ac:dyDescent="0.35">
-      <c r="A4" s="5">
-        <v>3</v>
-      </c>
-      <c r="B4" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="C4" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="D4" s="12" t="s">
-        <v>32</v>
-      </c>
-      <c r="E4" s="12" t="s">
-        <v>33</v>
-      </c>
-      <c r="F4" s="12" t="s">
-        <v>36</v>
-      </c>
-      <c r="G4" s="6">
-        <v>2026</v>
-      </c>
-      <c r="H4" s="7">
-        <v>3765771568</v>
-      </c>
-      <c r="I4" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="J4" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="K4" s="7">
-        <v>3000000000</v>
-      </c>
-      <c r="L4" s="7">
-        <v>3000000000</v>
-      </c>
-    </row>
-    <row r="5" spans="1:12" ht="46.5" x14ac:dyDescent="0.35">
-      <c r="A5" s="5">
-        <v>4</v>
-      </c>
-      <c r="B5" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="C5" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="D5" s="12"/>
-      <c r="E5" s="12"/>
-      <c r="F5" s="12"/>
-      <c r="G5" s="6">
-        <v>2026</v>
-      </c>
-      <c r="H5" s="7">
-        <v>1590994000</v>
-      </c>
-      <c r="I5" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="J5" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="K5" s="7">
-        <v>1000000000</v>
-      </c>
-      <c r="L5" s="7">
-        <v>1000000000</v>
-      </c>
-    </row>
-    <row r="6" spans="1:12" ht="31" x14ac:dyDescent="0.35">
-      <c r="A6" s="5">
-        <v>5</v>
-      </c>
-      <c r="B6" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="C6" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="D6" s="12" t="s">
-        <v>32</v>
-      </c>
-      <c r="E6" s="12"/>
-      <c r="F6" s="12"/>
-      <c r="G6" s="6">
-        <v>2026</v>
-      </c>
-      <c r="H6" s="7">
-        <v>526699800</v>
-      </c>
-      <c r="I6" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="J6" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="K6" s="7">
-        <v>500000000</v>
-      </c>
-      <c r="L6" s="7">
-        <v>500000000</v>
-      </c>
-    </row>
-    <row r="7" spans="1:12" ht="46.5" x14ac:dyDescent="0.35">
-      <c r="A7" s="5">
-        <v>6</v>
-      </c>
-      <c r="B7" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="C7" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="D7" s="12" t="s">
-        <v>32</v>
-      </c>
-      <c r="E7" s="12" t="s">
-        <v>34</v>
-      </c>
-      <c r="F7" s="12" t="s">
-        <v>36</v>
-      </c>
-      <c r="G7" s="6">
-        <v>2026</v>
-      </c>
-      <c r="H7" s="7">
-        <v>13236612376</v>
-      </c>
-      <c r="I7" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="J7" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="K7" s="7">
-        <v>10000000000</v>
-      </c>
-      <c r="L7" s="7">
-        <v>10000000000</v>
-      </c>
-    </row>
-    <row r="8" spans="1:12" ht="46.5" x14ac:dyDescent="0.35">
-      <c r="A8" s="5">
-        <v>7</v>
-      </c>
-      <c r="B8" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="C8" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="D8" s="12"/>
-      <c r="E8" s="12" t="s">
-        <v>26</v>
-      </c>
-      <c r="F8" s="12" t="s">
-        <v>37</v>
-      </c>
-      <c r="G8" s="6">
-        <v>2026</v>
-      </c>
-      <c r="H8" s="7">
-        <v>5780025934</v>
-      </c>
-      <c r="I8" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="J8" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="K8" s="7">
-        <v>5000000000</v>
-      </c>
-      <c r="L8" s="7">
-        <v>5000000000</v>
-      </c>
-    </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A9" s="8"/>
-      <c r="B9" s="9"/>
-      <c r="C9" s="10" t="s">
-        <v>27</v>
-      </c>
-      <c r="D9" s="12"/>
-      <c r="E9" s="17"/>
-      <c r="F9" s="17"/>
-      <c r="G9" s="9"/>
-      <c r="H9" s="11">
+      <c r="D9" s="13"/>
+      <c r="E9" s="19"/>
+      <c r="F9" s="19"/>
+      <c r="G9" s="10"/>
+      <c r="H9" s="12">
         <f>SUM(H2:H8)</f>
         <v>51103360596</v>
       </c>
-      <c r="I9" s="9"/>
-      <c r="J9" s="9"/>
-      <c r="K9" s="11">
+      <c r="I9" s="10"/>
+      <c r="J9" s="10"/>
+      <c r="K9" s="12">
         <f t="shared" ref="K9:L9" si="0">SUM(K2:K8)</f>
-        <v>30847233815</v>
-      </c>
-      <c r="L9" s="11">
+        <v>1347233815</v>
+      </c>
+      <c r="L9" s="12">
         <f t="shared" si="0"/>
-        <v>30847233815</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
